--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/output.xlsx
@@ -1139,14 +1139,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
   <x:sheetPr codeName="Лист3">
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
     <x:pageSetUpPr fitToPage="1"/>
   </x:sheetPr>
   <x:dimension ref="B2:H7"/>
   <x:sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <x:cols>
-    <x:col min="1" max="1" width="5.164062" style="0" customWidth="1"/>
-    <x:col min="2" max="8" width="10.832031" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="5.164062" customWidth="1"/>
+    <x:col min="2" max="8" width="10.832031" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1283,28 +1282,24 @@
       <x:formula>"VISA"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <x:pageSetup paperSize="9" fitToHeight="255" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed" r:id="rId1"/>
+  <x:pageSetup paperSize="9" fitToHeight="255" orientation="portrait" r:id="rId1"/>
   <x:headerFooter alignWithMargins="0"/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0100-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr codeName="Sheet1">
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
+  <x:sheetPr codeName="Sheet1"/>
   <x:dimension ref="B3:H370"/>
   <x:sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <x:cols>
-    <x:col min="1" max="1" width="4.332031" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="17.5" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="30.164062" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="15.332031" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="15.5" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="13.832031" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="4.332031" customWidth="1"/>
+    <x:col min="2" max="2" width="17.5" customWidth="1"/>
+    <x:col min="3" max="3" width="30.164062" customWidth="1"/>
+    <x:col min="4" max="4" width="15.332031" customWidth="1"/>
+    <x:col min="5" max="5" width="15.5" customWidth="1"/>
+    <x:col min="6" max="6" width="13.832031" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -1426,7 +1421,7 @@
       <x:c r="E9" s="22">
         <x:v>1004.8</x:v>
       </x:c>
-      <x:c r="F9" s="0">
+      <x:c r="F9">
         <x:v>1004.8</x:v>
       </x:c>
       <x:c r="G9" s="22">
@@ -1623,10 +1618,8 @@
     <x:mergeCell ref="B14:D14"/>
   </x:mergeCells>
   <x:phoneticPr fontId="0" type="noConversion"/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <x:pageSetup paperSize="9" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed" r:id="rId2"/>
+  <x:pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <x:headerFooter alignWithMargins="0"/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/output.xlsx
@@ -1144,8 +1144,8 @@
   <x:dimension ref="B2:H7"/>
   <x:sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <x:cols>
-    <x:col min="1" max="1" width="5.164062" customWidth="1"/>
-    <x:col min="2" max="8" width="10.832031" customWidth="1"/>
+    <x:col min="1" max="1" width="5.1640625" customWidth="1"/>
+    <x:col min="2" max="8" width="10.83203125" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1294,12 +1294,12 @@
   <x:dimension ref="B3:H370"/>
   <x:sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <x:cols>
-    <x:col min="1" max="1" width="4.332031" customWidth="1"/>
+    <x:col min="1" max="1" width="4.33203125" customWidth="1"/>
     <x:col min="2" max="2" width="17.5" customWidth="1"/>
-    <x:col min="3" max="3" width="30.164062" customWidth="1"/>
-    <x:col min="4" max="4" width="15.332031" customWidth="1"/>
+    <x:col min="3" max="3" width="30.1640625" customWidth="1"/>
+    <x:col min="4" max="4" width="15.33203125" customWidth="1"/>
     <x:col min="5" max="5" width="15.5" customWidth="1"/>
-    <x:col min="6" max="6" width="13.832031" customWidth="1"/>
+    <x:col min="6" max="6" width="13.83203125" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -1610,12 +1610,12 @@
     <x:mergeCell ref="G4:G5"/>
     <x:mergeCell ref="H4:H5"/>
     <x:mergeCell ref="B6:B12"/>
+    <x:mergeCell ref="B13:D13"/>
+    <x:mergeCell ref="B14:D14"/>
     <x:mergeCell ref="C7:D7"/>
     <x:mergeCell ref="C8:C9"/>
     <x:mergeCell ref="C10:D10"/>
     <x:mergeCell ref="C12:D12"/>
-    <x:mergeCell ref="B13:D13"/>
-    <x:mergeCell ref="B14:D14"/>
   </x:mergeCells>
   <x:phoneticPr fontId="0" type="noConversion"/>
   <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/output.xlsx
@@ -1497,16 +1497,16 @@
       <x:c r="C13" s="14"/>
       <x:c r="D13" s="14"/>
       <x:c r="E13" s="28">
-        <x:v>31399.65</x:v>
+        <x:v>31399.649999999998</x:v>
       </x:c>
       <x:c r="F13" s="29">
-        <x:v>31399.65</x:v>
+        <x:v>31399.649999999998</x:v>
       </x:c>
       <x:c r="G13" s="28">
-        <x:v>31399.65</x:v>
+        <x:v>31399.649999999998</x:v>
       </x:c>
       <x:c r="H13" s="30">
-        <x:v>31399.65</x:v>
+        <x:v>31399.649999999998</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1516,16 +1516,16 @@
       <x:c r="C14" s="34"/>
       <x:c r="D14" s="34"/>
       <x:c r="E14" s="25">
-        <x:v>31399.65</x:v>
+        <x:v>31399.649999999998</x:v>
       </x:c>
       <x:c r="F14" s="26">
-        <x:v>31399.65</x:v>
+        <x:v>31399.649999999998</x:v>
       </x:c>
       <x:c r="G14" s="25">
-        <x:v>31399.65</x:v>
+        <x:v>31399.649999999998</x:v>
       </x:c>
       <x:c r="H14" s="27">
-        <x:v>31399.65</x:v>
+        <x:v>31399.649999999998</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
